--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_16.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_16.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>PracticeTrials</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>IV2</t>
+          <t>Anxiety</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>1.152167039800315</v>
+        <v>-1.883955889608826</v>
       </c>
       <c r="C2">
-        <v>0.9729233822605937</v>
+        <v>1.741246144380086</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.4489955769147902</v>
+        <v>0.3887541326250892</v>
       </c>
       <c r="C3">
-        <v>-0.2703509018789599</v>
+        <v>-0.8564713315605897</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.3633498655362348</v>
+        <v>1.424275014675543</v>
       </c>
       <c r="C4">
-        <v>1.199605829150386</v>
+        <v>-0.91039374702562</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.5084144563615217</v>
+        <v>0.4662440253658942</v>
       </c>
       <c r="C5">
-        <v>-0.1056478784850178</v>
+        <v>0.4932714768349324</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.895506717692751</v>
+        <v>0.2821948523882841</v>
       </c>
       <c r="C6">
-        <v>0.07671470264081376</v>
+        <v>-1.135655520088712</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.5008843961198712</v>
+        <v>0.3200302329134109</v>
       </c>
       <c r="C7">
-        <v>-1.581303706188434</v>
+        <v>1.40706890589716</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>2.764286199525303</v>
+        <v>0.9726089169943466</v>
       </c>
       <c r="C8">
-        <v>0.07976222521020099</v>
+        <v>-1.433478068604906</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.5841573679036048</v>
+        <v>-0.524598761763138</v>
       </c>
       <c r="C9">
-        <v>-0.2214261325749749</v>
+        <v>-0.7186353831711852</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.9857062922850268</v>
+        <v>-1.572346225298717</v>
       </c>
       <c r="C10">
-        <v>-0.4432891092442933</v>
+        <v>1.435117718749241</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.604449441512203</v>
+        <v>0.5539288489980493</v>
       </c>
       <c r="C11">
-        <v>0.8662308069659336</v>
+        <v>-1.604199690876005</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.05245237764488251</v>
+        <v>-0.1172049605548381</v>
       </c>
       <c r="C12">
-        <v>-0.8193835280286844</v>
+        <v>0.7269572664005016</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.0875845206632174</v>
+        <v>0.1881881521777974</v>
       </c>
       <c r="C13">
-        <v>-0.9404918917474711</v>
+        <v>-1.327231823840046</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>1.573435565995876</v>
+        <v>0.2175523417298878</v>
       </c>
       <c r="C14">
-        <v>0.2606001551531966</v>
+        <v>0.1365980750728869</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>1.26164270707429</v>
+        <v>-0.36879180617635</v>
       </c>
       <c r="C15">
-        <v>-0.4084299562426575</v>
+        <v>-0.2489775030072975</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.9918542347265952</v>
+        <v>-1.292103432329366</v>
       </c>
       <c r="C16">
-        <v>1.191951435995084</v>
+        <v>-0.6342334141971875</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.4673521679038499</v>
+        <v>-1.051812696101755</v>
       </c>
       <c r="C17">
-        <v>0.3877517823166942</v>
+        <v>0.6396940756773463</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>2.124982613514247</v>
+        <v>0.4254896780937312</v>
       </c>
       <c r="C18">
-        <v>0.9865502021245669</v>
+        <v>0.06728045996999574</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.5178465249850351</v>
+        <v>-0.4790991446587413</v>
       </c>
       <c r="C19">
-        <v>-0.556681445993419</v>
+        <v>-0.4754595797742828</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.084522020549359</v>
+        <v>1.238865712610132</v>
       </c>
       <c r="C20">
-        <v>0.9191567049026586</v>
+        <v>-1.89802800960621</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.87292796212476</v>
+        <v>-1.10097840595705</v>
       </c>
       <c r="C21">
-        <v>-1.124168253531519</v>
+        <v>0.3255422593837535</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.6077517106337256</v>
+        <v>-2.043680862642538</v>
       </c>
       <c r="C22">
-        <v>-1.416724798914984</v>
+        <v>-0.3576389249522146</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.117787732168044</v>
+        <v>-0.7438804990839627</v>
       </c>
       <c r="C23">
-        <v>1.274352608476099</v>
+        <v>0.372762552866354</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.301099284231073</v>
+        <v>-0.6659008823579965</v>
       </c>
       <c r="C24">
-        <v>0.7883699755115379</v>
+        <v>-0.7603278432989786</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.6204064305044676</v>
+        <v>0.1356780233018487</v>
       </c>
       <c r="C25">
-        <v>0.4458269466263122</v>
+        <v>-0.7652071201807226</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.4575589427050248</v>
+        <v>-0.4062078820399928</v>
       </c>
       <c r="C26">
-        <v>-1.312605367474539</v>
+        <v>0.3243267901101888</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.584470974757188</v>
+        <v>-0.7364892465244737</v>
       </c>
       <c r="C27">
-        <v>-0.1932350693191526</v>
+        <v>-0.1008695553530445</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.024453197322409</v>
+        <v>0.6008640424805309</v>
       </c>
       <c r="C28">
-        <v>0.5893040581686521</v>
+        <v>0.883046402683305</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.235637189730569</v>
+        <v>-0.3229039637806427</v>
       </c>
       <c r="C29">
-        <v>-2.903762063494495</v>
+        <v>0.6416554351892606</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-1.503385097428029</v>
+        <v>0.4915701216808999</v>
       </c>
       <c r="C30">
-        <v>1.092577972489401</v>
+        <v>1.745815483492265</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.5012778296583139</v>
+        <v>-2.029126665914019</v>
       </c>
       <c r="C31">
-        <v>-2.559068928623482</v>
+        <v>2.565586653922182</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.9856689812912195</v>
+        <v>0.06159523008825142</v>
       </c>
       <c r="C32">
-        <v>1.275499392153956</v>
+        <v>-0.15125071725974</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>-0.2044855458256526</v>
+        <v>0.6496293475100625</v>
       </c>
       <c r="C33">
-        <v>0.1482324127124894</v>
+        <v>0.1779356772552869</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>1.565024588986787</v>
+        <v>-1.213511218368569</v>
       </c>
       <c r="C34">
-        <v>-0.7509403057266401</v>
+        <v>-0.355639949406128</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>1.578349353407256</v>
+        <v>-0.3829206957031543</v>
       </c>
       <c r="C35">
-        <v>-0.296647246587562</v>
+        <v>-0.9755936965181409</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.9632355757511963</v>
+        <v>-0.2669351810763454</v>
       </c>
       <c r="C36">
-        <v>-0.7054972660636597</v>
+        <v>-0.1476908019081183</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.5072649619445113</v>
+        <v>0.09286536653109594</v>
       </c>
       <c r="C37">
-        <v>-0.1858818077470978</v>
+        <v>-1.197026879987386</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.9475729512635029</v>
+        <v>1.461007221975235</v>
       </c>
       <c r="C38">
-        <v>1.168321617861814</v>
+        <v>-2.755603561608825</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>1.118417268983289</v>
+        <v>-0.4039011991117044</v>
       </c>
       <c r="C39">
-        <v>0.2729037696991486</v>
+        <v>0.4328065108327478</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.1673214026322879</v>
+        <v>-1.57998687555157</v>
       </c>
       <c r="C40">
-        <v>0.9648501814788998</v>
+        <v>-0.1177953158644583</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.8236791006522649</v>
+        <v>2.726809150140377</v>
       </c>
       <c r="C41">
-        <v>-2.05657229297524</v>
+        <v>-0.3596657510989762</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.5937961837102408</v>
+        <v>-0.1565366305168021</v>
       </c>
       <c r="C42">
-        <v>0.8213943986692006</v>
+        <v>0.7450426212760864</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.1420323306570629</v>
+        <v>-0.4316637458117361</v>
       </c>
       <c r="C43">
-        <v>-0.2008598512834108</v>
+        <v>0.1386156756480938</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.7766754976573489</v>
+        <v>-0.1423490410138971</v>
       </c>
       <c r="C44">
-        <v>-0.7842803320388546</v>
+        <v>-1.306157647164691</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.4333299079085014</v>
+        <v>-1.521138568076327</v>
       </c>
       <c r="C45">
-        <v>0.1705663157665992</v>
+        <v>0.1137337227471609</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.06416244438755132</v>
+        <v>-0.5115692468335751</v>
       </c>
       <c r="C46">
-        <v>-0.8130736348658673</v>
+        <v>-0.841033391991553</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>1.777019874282469</v>
+        <v>1.093581000274055</v>
       </c>
       <c r="C47">
-        <v>0.03007078377242148</v>
+        <v>-1.04260996634055</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-1.428846168967822</v>
+        <v>-0.1315079548078301</v>
       </c>
       <c r="C48">
-        <v>-1.271218600862283</v>
+        <v>0.2262047428947574</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-1.182753223885257</v>
+        <v>1.52787317795614</v>
       </c>
       <c r="C49">
-        <v>1.261993834108706</v>
+        <v>-1.545977682437344</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-1.096351423670845</v>
+        <v>-0.6022982672667141</v>
       </c>
       <c r="C50">
-        <v>0.9004248512374866</v>
+        <v>-0.2293341085130022</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.4176718386120552</v>
+        <v>-0.5904411074079025</v>
       </c>
       <c r="C51">
-        <v>-0.602903336685409</v>
+        <v>0.5819059713697845</v>
       </c>
     </row>
   </sheetData>
